--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_15_24.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_15_24.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>471616.1075085519</v>
+        <v>458450.9695147759</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8034137.820949661</v>
+        <v>8041589.773721423</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17786623.82965985</v>
+        <v>17785260.94054101</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5648257.284105356</v>
+        <v>5648013.351828624</v>
       </c>
     </row>
     <row r="11">
@@ -649,7 +649,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -758,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1281,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -1490,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1846,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.498001805406602e-16</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1931,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.498001805406602e-16</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1995,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.191891195797325e-16</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2083,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2119,13 +2119,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2153,13 +2153,13 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2226,16 +2226,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.885780586188048e-16</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2396,16 +2396,16 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2.914335439641036e-16</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2432,13 +2432,13 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2508,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -2520,16 +2520,16 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.665334536937735e-16</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -2590,16 +2590,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2633,16 +2633,16 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2684,10 +2684,10 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2763,13 +2763,13 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2785,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -2827,13 +2827,13 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -2915,19 +2915,19 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2997,16 +2997,16 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3028,10 +3028,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3076,10 +3076,10 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -3107,16 +3107,16 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3158,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3234,13 +3234,13 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3301,10 +3301,10 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -3332,13 +3332,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3350,7 +3350,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3401,7 +3401,7 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3429,10 +3429,10 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3468,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -3496,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3544,10 +3544,10 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -3696,16 +3696,16 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -3775,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -4289,19 +4289,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -4328,37 +4328,37 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -4371,25 +4371,25 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -4763,28 +4763,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -4820,19 +4820,19 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4842,28 +4842,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -4890,28 +4890,28 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4924,28 +4924,28 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -5079,25 +5079,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -5127,28 +5127,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5498,10 +5498,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -5577,13 +5577,13 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -5638,7 +5638,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>8.326672684688674e-17</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -5662,19 +5662,19 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -5723,49 +5723,49 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.665334536937735e-16</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2.775557561562891e-16</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1.387778780781446e-16</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -5820,46 +5820,46 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -5896,49 +5896,49 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>6.661338147750939e-16</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>6.661338147750939e-16</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -5990,34 +5990,34 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -6027,25 +6027,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5.551115123125783e-16</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>5.551115123125783e-16</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>5.551115123125783e-16</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>5.551115123125783e-16</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>3.608224830031759e-16</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>2.862293735361732e-16</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.862293735361732e-16</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -6063,40 +6063,40 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>5.551115123125783e-16</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>5.551115123125783e-16</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>5.551115123125783e-16</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>5.551115123125783e-16</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>5.551115123125783e-16</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.551115123125783e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -6133,43 +6133,43 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.942890293094024e-16</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -6230,19 +6230,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -6273,16 +6273,16 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.838806884535416e-16</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -6309,25 +6309,25 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -6385,34 +6385,34 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -6428,25 +6428,25 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -6461,34 +6461,34 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -6501,37 +6501,37 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -6543,34 +6543,34 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -6580,31 +6580,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -6616,40 +6616,40 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -6659,31 +6659,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -6701,7 +6701,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -6719,16 +6719,16 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -6738,34 +6738,34 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -6777,37 +6777,37 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -6817,37 +6817,37 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -6859,34 +6859,34 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -6896,28 +6896,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -6944,28 +6944,28 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -6975,31 +6975,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -7014,37 +7014,37 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -7054,37 +7054,37 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -7096,34 +7096,34 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -7151,58 +7151,58 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -7212,16 +7212,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -7257,31 +7257,31 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -7330,22 +7330,22 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -7409,7 +7409,7 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -7449,7 +7449,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -7491,7 +7491,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7503,22 +7503,22 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -7567,7 +7567,7 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -7576,7 +7576,7 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8196,22 +8196,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K5" t="n">
-        <v>219.5784791856841</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L5" t="n">
-        <v>235.132012959937</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M5" t="n">
-        <v>229.6403387549109</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N5" t="n">
-        <v>228.6957470136763</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O5" t="n">
-        <v>229.420869713144</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P5" t="n">
-        <v>230.6549002778826</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q5" t="n">
         <v>212.3149906599047</v>
@@ -8275,25 +8275,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K6" t="n">
-        <v>137.4941087856797</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L6" t="n">
-        <v>138.0873514779874</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M6" t="n">
-        <v>141.5890339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N6" t="n">
-        <v>130.7822875550314</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O6" t="n">
-        <v>142.084480293501</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P6" t="n">
-        <v>133.5636715652736</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q6" t="n">
-        <v>139.7072080482857</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R6" t="n">
         <v>45.52166981132082</v>
@@ -8357,16 +8357,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L7" t="n">
-        <v>134.6165779205826</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M7" t="n">
-        <v>138.6431118164575</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N7" t="n">
-        <v>127.4095936455611</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O7" t="n">
-        <v>138.2016532059411</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P7" t="n">
         <v>135.0065633140411</v>
@@ -8433,22 +8433,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>219.0671073263876</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L8" t="n">
-        <v>234.4976109498867</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M8" t="n">
-        <v>228.9344442825491</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N8" t="n">
-        <v>227.9784304307618</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O8" t="n">
-        <v>228.7435280046013</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P8" t="n">
-        <v>230.0768048004957</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8512,25 +8512,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>137.1467785970005</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L9" t="n">
-        <v>137.6203231761006</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>141.0440339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
-        <v>130.2228630267295</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>141.5727161425577</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
-        <v>133.152935716217</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>139.4326420105498</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,16 +8594,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>134.3484795599268</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M10" t="n">
-        <v>138.36043968531</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N10" t="n">
-        <v>127.1336428258889</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O10" t="n">
-        <v>137.9467679600395</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P10" t="n">
         <v>135.0065633140411</v>
@@ -8667,28 +8667,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K11" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L11" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M11" t="n">
-        <v>113.8736452875742</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N11" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O11" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P11" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q11" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,28 +8746,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K12" t="n">
-        <v>80.53195784228352</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L12" t="n">
-        <v>61.49470996855343</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M12" t="n">
-        <v>52.20903392201834</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N12" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O12" t="n">
-        <v>58.15515953878407</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P12" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q12" t="n">
-        <v>94.67837785960641</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8828,22 +8828,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L13" t="n">
-        <v>90.64844677304158</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M13" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N13" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O13" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P13" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,28 +8904,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K14" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L14" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M14" t="n">
-        <v>113.8736452875742</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N14" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O14" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P14" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q14" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8983,28 +8983,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K15" t="n">
-        <v>80.53195784228352</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L15" t="n">
-        <v>61.49470996855343</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M15" t="n">
-        <v>52.20903392201834</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N15" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O15" t="n">
-        <v>58.15515953878407</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P15" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q15" t="n">
-        <v>94.67837785960641</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9065,22 +9065,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K16" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L16" t="n">
-        <v>90.64844677304158</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M16" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N16" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O16" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P16" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9141,28 +9141,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K17" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L17" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M17" t="n">
-        <v>113.8736452875742</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N17" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O17" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P17" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q17" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9220,28 +9220,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K18" t="n">
-        <v>80.5319578422835</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L18" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M18" t="n">
-        <v>52.20903392201833</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N18" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O18" t="n">
-        <v>58.15515953878406</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P18" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q18" t="n">
-        <v>94.6783778596064</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9302,22 +9302,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L19" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M19" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N19" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O19" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P19" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q19" t="n">
         <v>65.34295837775146</v>
@@ -9378,28 +9378,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K20" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L20" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M20" t="n">
-        <v>113.8736452875742</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N20" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O20" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P20" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q20" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9457,28 +9457,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K21" t="n">
-        <v>80.5319578422835</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L21" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M21" t="n">
-        <v>52.20903392201833</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N21" t="n">
-        <v>39.03666491352196</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O21" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P21" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q21" t="n">
-        <v>94.6783778596064</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9539,22 +9539,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L22" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M22" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N22" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O22" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P22" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9615,28 +9615,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K23" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L23" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M23" t="n">
-        <v>113.8736452875742</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N23" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O23" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P23" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q23" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9694,28 +9694,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K24" t="n">
-        <v>80.5319578422835</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L24" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M24" t="n">
-        <v>52.20903392201833</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N24" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O24" t="n">
-        <v>58.15515953878406</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P24" t="n">
-        <v>66.2029923199906</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q24" t="n">
-        <v>94.6783778596064</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9776,22 +9776,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>94.44440571151898</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L25" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M25" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N25" t="n">
-        <v>82.15365921933152</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O25" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P25" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9852,28 +9852,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K26" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L26" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M26" t="n">
-        <v>113.8736452875742</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N26" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O26" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P26" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q26" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,28 +9931,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K27" t="n">
-        <v>80.53195784228352</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L27" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M27" t="n">
-        <v>52.20903392201832</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N27" t="n">
-        <v>39.03666491352196</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O27" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P27" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q27" t="n">
-        <v>94.67837785960641</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10013,22 +10013,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L28" t="n">
-        <v>90.64844677304156</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M28" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N28" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O28" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P28" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10089,28 +10089,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K29" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L29" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M29" t="n">
-        <v>113.8736452875742</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N29" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O29" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P29" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q29" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,28 +10168,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K30" t="n">
-        <v>80.5319578422835</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L30" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M30" t="n">
-        <v>52.20903392201833</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N30" t="n">
-        <v>39.03666491352196</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O30" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P30" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q30" t="n">
-        <v>94.67837785960641</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10250,22 +10250,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K31" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L31" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M31" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N31" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O31" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P31" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10326,28 +10326,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K32" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L32" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M32" t="n">
-        <v>113.8736452875742</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N32" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O32" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P32" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q32" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10405,28 +10405,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K33" t="n">
-        <v>80.5319578422835</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L33" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M33" t="n">
-        <v>52.20903392201832</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N33" t="n">
-        <v>39.03666491352196</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O33" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P33" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q33" t="n">
-        <v>94.6783778596064</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10487,22 +10487,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K34" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L34" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M34" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N34" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O34" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P34" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10563,28 +10563,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K35" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L35" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M35" t="n">
-        <v>113.8736452875742</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N35" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O35" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P35" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q35" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,28 +10642,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K36" t="n">
-        <v>80.53195784228352</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L36" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M36" t="n">
-        <v>52.20903392201832</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N36" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O36" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P36" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q36" t="n">
-        <v>94.6783778596064</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10724,22 +10724,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K37" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L37" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M37" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N37" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O37" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P37" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10800,28 +10800,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K38" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L38" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M38" t="n">
-        <v>113.8736452875742</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N38" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O38" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P38" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q38" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10879,28 +10879,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>93.30682477987425</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K39" t="n">
-        <v>80.5319578422835</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L39" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M39" t="n">
-        <v>52.20903392201833</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N39" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O39" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P39" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q39" t="n">
-        <v>94.67837785960641</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10961,22 +10961,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K40" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L40" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M40" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N40" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O40" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P40" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q40" t="n">
         <v>65.34295837775146</v>
@@ -11037,28 +11037,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K41" t="n">
-        <v>135.7134942610609</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L41" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M41" t="n">
-        <v>113.8736452875742</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N41" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O41" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P41" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q41" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,28 +11116,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>93.30682477987425</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K42" t="n">
-        <v>80.53195784228352</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L42" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M42" t="n">
-        <v>52.20903392201833</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N42" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O42" t="n">
-        <v>58.15515953878406</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P42" t="n">
-        <v>66.20299231999061</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q42" t="n">
-        <v>94.67837785960641</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11198,22 +11198,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K43" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L43" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M43" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N43" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O43" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P43" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q43" t="n">
         <v>65.34295837775146</v>
@@ -11274,28 +11274,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K44" t="n">
-        <v>135.713494261061</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L44" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M44" t="n">
-        <v>113.8736452875742</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N44" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O44" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P44" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q44" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R44" t="n">
         <v>65.71641987298243</v>
@@ -11353,28 +11353,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K45" t="n">
-        <v>80.5319578422835</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L45" t="n">
-        <v>61.49470996855342</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M45" t="n">
-        <v>52.20903392201833</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N45" t="n">
-        <v>39.03666491352198</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O45" t="n">
-        <v>58.15515953878408</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P45" t="n">
-        <v>66.20299231999063</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q45" t="n">
-        <v>94.67837785960641</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11435,22 +11435,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K46" t="n">
-        <v>94.44440571151901</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L46" t="n">
-        <v>90.64844677304157</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M46" t="n">
-        <v>92.2848823082608</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N46" t="n">
-        <v>82.15365921933153</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O46" t="n">
-        <v>96.40047287807229</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P46" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q46" t="n">
         <v>65.34295837775146</v>
@@ -22756,7 +22756,7 @@
         <v>6.876045741711437</v>
       </c>
       <c r="G5" t="n">
-        <v>15.29871741463254</v>
+        <v>15.30273751513505</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -22993,7 +22993,7 @@
         <v>6.876045741711437</v>
       </c>
       <c r="G8" t="n">
-        <v>15.29469731413002</v>
+        <v>15.30273751513505</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -23230,13 +23230,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H11" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I11" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,16 +23263,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S11" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T11" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U11" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,13 +23309,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H12" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I12" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S12" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T12" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,16 +23388,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H13" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I13" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J13" t="n">
-        <v>72.32303257568917</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,19 +23418,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R13" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S13" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T13" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U13" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,13 +23467,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H14" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I14" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,16 +23500,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S14" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T14" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U14" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,13 +23546,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H15" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I15" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S15" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T15" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H16" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I16" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J16" t="n">
-        <v>72.32303257568917</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23655,19 +23655,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R16" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S16" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T16" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U16" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,13 +23704,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H17" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I17" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S17" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T17" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U17" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H18" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I18" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S18" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T18" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,16 +23862,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H19" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I19" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J19" t="n">
-        <v>72.32303257568917</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23892,19 +23892,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R19" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S19" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T19" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U19" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,13 +23941,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H20" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I20" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,16 +23974,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S20" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T20" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U20" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,13 +24020,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H21" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I21" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S21" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T21" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,16 +24099,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H22" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I22" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J22" t="n">
-        <v>72.32303257568917</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24129,19 +24129,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R22" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S22" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T22" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U22" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H23" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I23" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,16 +24211,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S23" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T23" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U23" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,13 +24257,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H24" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I24" t="n">
-        <v>77.17729322877355</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>78.12255113377522</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S24" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T24" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,16 +24336,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H25" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I25" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J25" t="n">
-        <v>72.32303257568917</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24366,19 +24366,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R25" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S25" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T25" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U25" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,13 +24415,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H26" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I26" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,19 +24448,19 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S26" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T26" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U26" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V26" t="n">
-        <v>327.7522584701348</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W26" t="n">
         <v>349.240968717413</v>
@@ -24494,13 +24494,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H27" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I27" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,16 +24527,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S27" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T27" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,16 +24573,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H28" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I28" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J28" t="n">
-        <v>72.32303257568917</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24603,19 +24603,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R28" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S28" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T28" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U28" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,13 +24652,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H29" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I29" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,16 +24685,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S29" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T29" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U29" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,13 +24731,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H30" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I30" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,16 +24764,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>78.12255113377519</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S30" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T30" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,16 +24810,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H31" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I31" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J31" t="n">
-        <v>72.32303257568917</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -24840,19 +24840,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R31" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S31" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T31" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U31" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,13 +24889,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H32" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I32" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,19 +24922,19 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S32" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T32" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U32" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V32" t="n">
-        <v>327.752258470135</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
         <v>349.240968717413</v>
@@ -24968,13 +24968,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H33" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I33" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S33" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T33" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,16 +25047,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H34" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I34" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J34" t="n">
-        <v>72.32303257568917</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -25077,19 +25077,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R34" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S34" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T34" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U34" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,13 +25126,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H35" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I35" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,16 +25159,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S35" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T35" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U35" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,13 +25205,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H36" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I36" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S36" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T36" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,16 +25284,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H37" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I37" t="n">
-        <v>146.5026060747992</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J37" t="n">
-        <v>72.32303257568917</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -25314,19 +25314,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R37" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S37" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T37" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U37" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,13 +25363,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H38" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I38" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S38" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T38" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U38" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,13 +25442,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H39" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I39" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S39" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T39" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,16 +25521,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H40" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I40" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J40" t="n">
-        <v>72.32303257568917</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -25551,19 +25551,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R40" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S40" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T40" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U40" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,13 +25600,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H41" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I41" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,16 +25633,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S41" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T41" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U41" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,13 +25679,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H42" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I42" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25712,16 +25712,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S42" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T42" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,16 +25758,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H43" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I43" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J43" t="n">
-        <v>72.32303257568917</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -25788,19 +25788,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R43" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S43" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T43" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U43" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,13 +25837,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H44" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I44" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25870,16 +25870,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S44" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T44" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U44" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,13 +25916,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H45" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I45" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S45" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T45" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,16 +25995,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H46" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I46" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J46" t="n">
-        <v>72.32303257568918</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -26025,19 +26025,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R46" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S46" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T46" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U46" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1022625.276214163</v>
+        <v>1022798.34367318</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1022452.208755146</v>
+        <v>1022798.34367318</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>310803.5129388982</v>
+        <v>310719.3407473862</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>310803.5129388982</v>
+        <v>310719.3407473862</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>310803.5129388982</v>
+        <v>310719.3407473862</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>310803.5129388982</v>
+        <v>310719.3407473862</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>310803.5129388982</v>
+        <v>310719.3407473862</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>310803.5129388982</v>
+        <v>310719.3407473862</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>310803.5129388982</v>
+        <v>310719.3407473862</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>310803.5129388982</v>
+        <v>310719.3407473862</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>310803.5129388982</v>
+        <v>310719.3407473862</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>310803.5129388982</v>
+        <v>310719.3407473862</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>310803.5129388982</v>
+        <v>310719.3407473862</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>310803.5129388982</v>
+        <v>310719.3407473862</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>491565.8032302229</v>
+      </c>
+      <c r="C2" t="n">
         <v>491565.803230223</v>
       </c>
-      <c r="C2" t="n">
-        <v>491565.9952302231</v>
-      </c>
       <c r="D2" t="n">
-        <v>491566.1872302228</v>
+        <v>491565.8032302231</v>
       </c>
       <c r="E2" t="n">
-        <v>137157.3519974595</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="F2" t="n">
-        <v>137157.3519974595</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="G2" t="n">
-        <v>137157.3519974595</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="H2" t="n">
-        <v>137157.3519974595</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="I2" t="n">
-        <v>137157.3519974595</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="J2" t="n">
-        <v>137157.3519974595</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="K2" t="n">
-        <v>137157.3519974595</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="L2" t="n">
-        <v>137157.3519974595</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="M2" t="n">
-        <v>137157.3519974595</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="N2" t="n">
-        <v>137157.3519974595</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="O2" t="n">
-        <v>137157.3519974595</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="P2" t="n">
-        <v>137157.3519974595</v>
+        <v>137184.6577798363</v>
       </c>
     </row>
     <row r="3">
@@ -26316,19 +26316,19 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>910.602</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>856.4139999999934</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>130954.689</v>
+        <v>133100.0000000001</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1.640049540618805e-11</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>425523.1391661035</v>
+        <v>427717.1737329711</v>
       </c>
       <c r="C4" t="n">
-        <v>425265.1323448123</v>
+        <v>427717.1737329711</v>
       </c>
       <c r="D4" t="n">
-        <v>425007.1255235209</v>
+        <v>427717.1737329711</v>
       </c>
       <c r="E4" t="n">
-        <v>47918.58827710071</v>
+        <v>49082.27614186519</v>
       </c>
       <c r="F4" t="n">
-        <v>47918.58827710071</v>
+        <v>49082.27614186519</v>
       </c>
       <c r="G4" t="n">
-        <v>47918.58827710071</v>
+        <v>49082.27614186519</v>
       </c>
       <c r="H4" t="n">
-        <v>47918.5882771007</v>
+        <v>49082.27614186519</v>
       </c>
       <c r="I4" t="n">
-        <v>47918.5882771007</v>
+        <v>49082.27614186519</v>
       </c>
       <c r="J4" t="n">
-        <v>47918.5882771007</v>
+        <v>49082.27614186519</v>
       </c>
       <c r="K4" t="n">
-        <v>47918.5882771007</v>
+        <v>49082.27614186519</v>
       </c>
       <c r="L4" t="n">
-        <v>47918.5882771007</v>
+        <v>49082.27614186519</v>
       </c>
       <c r="M4" t="n">
-        <v>47918.58827710071</v>
+        <v>49082.27614186519</v>
       </c>
       <c r="N4" t="n">
-        <v>47918.5882771007</v>
+        <v>49082.27614186519</v>
       </c>
       <c r="O4" t="n">
-        <v>47918.58827710071</v>
+        <v>49082.27614186519</v>
       </c>
       <c r="P4" t="n">
-        <v>47918.5882771007</v>
+        <v>49082.27614186519</v>
       </c>
     </row>
     <row r="5">
@@ -26420,46 +26420,46 @@
         <v>33627.6</v>
       </c>
       <c r="C5" t="n">
-        <v>33649.4</v>
+        <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>33671.2</v>
+        <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="F5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="G5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="H5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="I5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="J5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="K5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="L5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="M5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="N5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="O5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="P5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32415.06406411945</v>
+        <v>30221.02949725177</v>
       </c>
       <c r="C6" t="n">
-        <v>31740.86088541082</v>
+        <v>30221.02949725182</v>
       </c>
       <c r="D6" t="n">
-        <v>32031.44770670189</v>
+        <v>30221.02949725194</v>
       </c>
       <c r="E6" t="n">
-        <v>-45312.9252796412</v>
+        <v>-48609.23046703728</v>
       </c>
       <c r="F6" t="n">
-        <v>85641.76372035884</v>
+        <v>84490.76953296279</v>
       </c>
       <c r="G6" t="n">
-        <v>85641.76372035872</v>
+        <v>84490.76953296279</v>
       </c>
       <c r="H6" t="n">
-        <v>85641.76372035878</v>
+        <v>84490.76953296279</v>
       </c>
       <c r="I6" t="n">
-        <v>85641.76372035878</v>
+        <v>84490.76953296279</v>
       </c>
       <c r="J6" t="n">
-        <v>85641.76372035881</v>
+        <v>84490.76953296279</v>
       </c>
       <c r="K6" t="n">
-        <v>85641.76372035884</v>
+        <v>84490.76953296279</v>
       </c>
       <c r="L6" t="n">
-        <v>85641.76372035875</v>
+        <v>84490.76953296279</v>
       </c>
       <c r="M6" t="n">
-        <v>85641.76372035881</v>
+        <v>84490.76953296279</v>
       </c>
       <c r="N6" t="n">
-        <v>85641.76372035884</v>
+        <v>84490.76953296279</v>
       </c>
       <c r="O6" t="n">
-        <v>85641.76372035881</v>
+        <v>84490.76953296279</v>
       </c>
       <c r="P6" t="n">
-        <v>85641.76372035878</v>
+        <v>84490.76953296279</v>
       </c>
     </row>
   </sheetData>
@@ -26678,46 +26678,46 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9999999999999991</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.999999999999992</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="F3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="G3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="H3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="I3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="J3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="K3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="L3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="M3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="N3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="O3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="P3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
     </row>
     <row r="4">
@@ -26745,25 +26745,25 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26895,16 +26895,16 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>163</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -26916,25 +26916,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,28 +26944,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -26980,13 +26980,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27556,13 +27556,13 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>339.4336312614958</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I5" t="n">
-        <v>210.3209046457828</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J5" t="n">
-        <v>11.60808834958739</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -27583,19 +27583,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.556573586404101</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R5" t="n">
-        <v>149.6165903029587</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S5" t="n">
-        <v>208.9284615460443</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T5" t="n">
-        <v>223.0782515741816</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U5" t="n">
-        <v>251.3453312997963</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V5" t="n">
         <v>327.7522584701349</v>
@@ -27632,16 +27632,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G6" t="n">
-        <v>137.3413662198144</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H6" t="n">
-        <v>112.2146706515908</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I6" t="n">
-        <v>89.32257624764149</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5433743451257814</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -27665,16 +27665,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>100.0242869828318</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S6" t="n">
-        <v>171.6432182736492</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T6" t="n">
-        <v>200.1560588835009</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U6" t="n">
-        <v>225.9412405715408</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V6" t="n">
         <v>232.8005871494253</v>
@@ -27711,19 +27711,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G7" t="n">
-        <v>167.9891760797702</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H7" t="n">
-        <v>162.2111397205543</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I7" t="n">
-        <v>155.3962454190616</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J7" t="n">
-        <v>93.23168831339409</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K7" t="n">
-        <v>22.05998362916154</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -27738,22 +27738,22 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.503342374450774</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q7" t="n">
-        <v>86.01104325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R7" t="n">
-        <v>177.2123094099564</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S7" t="n">
-        <v>223.9851718074641</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T7" t="n">
-        <v>227.9378845102487</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U7" t="n">
-        <v>286.3189309958352</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V7" t="n">
         <v>252.137643323828</v>
@@ -27793,13 +27793,13 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>339.3924604072245</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I8" t="n">
-        <v>210.1659197211597</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
-        <v>11.26688734456227</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -27820,19 +27820,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.1224479582634</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>149.3640626647678</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S8" t="n">
-        <v>208.8368535058434</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T8" t="n">
-        <v>223.0606535842319</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U8" t="n">
-        <v>251.3450096917561</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
@@ -27869,16 +27869,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>137.3392152764182</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H9" t="n">
-        <v>112.1938970666851</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I9" t="n">
-        <v>89.24851964386791</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3401573639937074</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -27902,16 +27902,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>99.89073981302049</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S9" t="n">
-        <v>171.6032654434605</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T9" t="n">
-        <v>200.1473890721801</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U9" t="n">
-        <v>225.9410990621069</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V9" t="n">
         <v>232.8005871494253</v>
@@ -27948,19 +27948,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.9873728010817</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H10" t="n">
-        <v>162.1951069336691</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>155.3420159108648</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J10" t="n">
-        <v>93.1041965101154</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
-        <v>21.85047543244023</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -27975,22 +27975,22 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.285244013795038</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>85.86004325169438</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R10" t="n">
-        <v>177.1312274427433</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S10" t="n">
-        <v>223.9537455779559</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T10" t="n">
-        <v>227.9301795922159</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U10" t="n">
-        <v>286.3188326351794</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V10" t="n">
         <v>252.137643323828</v>
@@ -31196,49 +31196,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004020100502512556</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04117085427135673</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1549849246231155</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3412010050251254</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.511371859296482</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6344020100502508</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7058944723618084</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7173165829145722</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.677341708542713</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5780954773869341</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4341256281407031</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2525276381909546</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.09160804020100496</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01759798994974872</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0003216080402010044</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31275,49 +31275,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002150943396226413</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02077358490566036</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07405660377358485</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2032169811320753</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.347330188679245</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4670283018867921</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5449999999999995</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5594245283018864</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5117641509433958</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4107358490566034</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2745660377358489</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1335471698113207</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03995283018867919</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008669811320754707</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001415094339622641</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31354,49 +31354,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001803278688524588</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0160327868852459</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05422950819672127</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1274918032786884</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2095081967213112</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2680983606557375</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2826721311475406</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2759508196721311</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2548852459016392</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2180983606557374</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1509999999999999</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.08108196721311466</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03142622950819668</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007704918032786875</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>9.836065573770494e-05</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31433,49 +31433,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.008040201005025087</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08234170854271319</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3099698492462299</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6824020100502486</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.022743718592961</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.268804020100497</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.411788944723612</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.43463316582914</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.354683417085422</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.156190954773864</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8682512562814034</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5050552763819076</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1832160804020093</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03519597989949733</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0006432160804020067</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31512,49 +31512,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004301886792452813</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0415471698113206</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1481132075471692</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4064339622641494</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6946603773584878</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9340566037735812</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.089999999999995</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.118849056603769</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.023528301886788</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8214716981132043</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.549132075471696</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2670943396226405</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.07990566037735811</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01733962264150936</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0002830188679245273</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31591,49 +31591,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003606557377049165</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.03206557377049169</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1084590163934422</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.254983606557376</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4190163934426211</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5361967213114732</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5653442622950795</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5519016393442604</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5097704918032767</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4361967213114734</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3019999999999987</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1621639344262288</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.06285245901639316</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0154098360655737</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0001967213114754092</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H11" t="n">
-        <v>6.793190954773865</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I11" t="n">
-        <v>25.57251256281407</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J11" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K11" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L11" t="n">
-        <v>104.6763316582915</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M11" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N11" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O11" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P11" t="n">
-        <v>95.38575376884421</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q11" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R11" t="n">
-        <v>41.66706030150753</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S11" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T11" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U11" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,49 +31749,49 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H12" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I12" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J12" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K12" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L12" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M12" t="n">
-        <v>89.92499999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N12" t="n">
-        <v>92.30504716981132</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O12" t="n">
-        <v>84.44108490566038</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P12" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q12" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R12" t="n">
-        <v>22.03528301886793</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S12" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T12" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U12" t="n">
-        <v>0.02334905660377359</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H13" t="n">
-        <v>2.645409836065575</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I13" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J13" t="n">
-        <v>21.0361475409836</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K13" t="n">
-        <v>34.56885245901638</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L13" t="n">
-        <v>44.23622950819672</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M13" t="n">
-        <v>46.64090163934425</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N13" t="n">
-        <v>45.53188524590166</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O13" t="n">
-        <v>42.0560655737705</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P13" t="n">
-        <v>35.98622950819669</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q13" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R13" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S13" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T13" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01622950819672132</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H14" t="n">
-        <v>6.793190954773865</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I14" t="n">
-        <v>25.57251256281407</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J14" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K14" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L14" t="n">
-        <v>104.6763316582915</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M14" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N14" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O14" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P14" t="n">
-        <v>95.38575376884421</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q14" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R14" t="n">
-        <v>41.66706030150753</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S14" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T14" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U14" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,49 +31986,49 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H15" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I15" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J15" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K15" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L15" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M15" t="n">
-        <v>89.92499999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N15" t="n">
-        <v>92.30504716981132</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O15" t="n">
-        <v>84.44108490566038</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P15" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q15" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R15" t="n">
-        <v>22.03528301886793</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S15" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T15" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U15" t="n">
-        <v>0.02334905660377359</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H16" t="n">
-        <v>2.645409836065575</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I16" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J16" t="n">
-        <v>21.0361475409836</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K16" t="n">
-        <v>34.56885245901638</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L16" t="n">
-        <v>44.23622950819672</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M16" t="n">
-        <v>46.64090163934425</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N16" t="n">
-        <v>45.53188524590166</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O16" t="n">
-        <v>42.0560655737705</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P16" t="n">
-        <v>35.98622950819669</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q16" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R16" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S16" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T16" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U16" t="n">
-        <v>0.01622950819672132</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H17" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I17" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J17" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K17" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L17" t="n">
-        <v>104.6763316582915</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M17" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N17" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O17" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P17" t="n">
-        <v>95.38575376884424</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q17" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R17" t="n">
-        <v>41.66706030150755</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S17" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T17" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U17" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,49 +32223,49 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H18" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I18" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J18" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K18" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L18" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M18" t="n">
-        <v>89.92499999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N18" t="n">
-        <v>92.30504716981135</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O18" t="n">
-        <v>84.44108490566038</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P18" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q18" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R18" t="n">
-        <v>22.03528301886794</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S18" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T18" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0233490566037736</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H19" t="n">
-        <v>2.645409836065576</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I19" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J19" t="n">
-        <v>21.03614754098361</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K19" t="n">
-        <v>34.56885245901639</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L19" t="n">
-        <v>44.23622950819673</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M19" t="n">
-        <v>46.64090163934426</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N19" t="n">
-        <v>45.53188524590167</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O19" t="n">
-        <v>42.05606557377051</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P19" t="n">
-        <v>35.98622950819671</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q19" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R19" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S19" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T19" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U19" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H20" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I20" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J20" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K20" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L20" t="n">
-        <v>104.6763316582915</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M20" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N20" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O20" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P20" t="n">
-        <v>95.38575376884424</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q20" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R20" t="n">
-        <v>41.66706030150755</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S20" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T20" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U20" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,49 +32460,49 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H21" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I21" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J21" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K21" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L21" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M21" t="n">
-        <v>89.92499999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N21" t="n">
-        <v>92.30504716981135</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O21" t="n">
-        <v>84.44108490566038</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P21" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q21" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R21" t="n">
-        <v>22.03528301886794</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S21" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T21" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0233490566037736</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H22" t="n">
-        <v>2.645409836065576</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I22" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J22" t="n">
-        <v>21.03614754098361</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K22" t="n">
-        <v>34.56885245901639</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L22" t="n">
-        <v>44.23622950819673</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M22" t="n">
-        <v>46.64090163934426</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N22" t="n">
-        <v>45.53188524590167</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O22" t="n">
-        <v>42.05606557377051</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P22" t="n">
-        <v>35.98622950819671</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q22" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R22" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S22" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T22" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U22" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H23" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I23" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J23" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K23" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L23" t="n">
-        <v>104.6763316582915</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M23" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N23" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O23" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P23" t="n">
-        <v>95.38575376884424</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q23" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R23" t="n">
-        <v>41.66706030150755</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S23" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T23" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U23" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,49 +32697,49 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H24" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I24" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J24" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K24" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L24" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M24" t="n">
-        <v>89.92499999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N24" t="n">
-        <v>92.30504716981135</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O24" t="n">
-        <v>84.44108490566038</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P24" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q24" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R24" t="n">
-        <v>22.03528301886794</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S24" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T24" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0233490566037736</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H25" t="n">
-        <v>2.645409836065576</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I25" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J25" t="n">
-        <v>21.03614754098361</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K25" t="n">
-        <v>34.56885245901639</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L25" t="n">
-        <v>44.23622950819673</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M25" t="n">
-        <v>46.64090163934426</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N25" t="n">
-        <v>45.53188524590167</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O25" t="n">
-        <v>42.05606557377051</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P25" t="n">
-        <v>35.98622950819671</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q25" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R25" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S25" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T25" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U25" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H26" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I26" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J26" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K26" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L26" t="n">
-        <v>104.6763316582915</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M26" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N26" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O26" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P26" t="n">
-        <v>95.38575376884424</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q26" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R26" t="n">
-        <v>41.66706030150755</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S26" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T26" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U26" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,49 +32934,49 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H27" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I27" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J27" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K27" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L27" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M27" t="n">
-        <v>89.92499999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N27" t="n">
-        <v>92.30504716981135</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O27" t="n">
-        <v>84.44108490566038</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P27" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q27" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R27" t="n">
-        <v>22.03528301886794</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S27" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T27" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0233490566037736</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H28" t="n">
-        <v>2.645409836065576</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I28" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J28" t="n">
-        <v>21.03614754098361</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K28" t="n">
-        <v>34.56885245901639</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L28" t="n">
-        <v>44.23622950819673</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M28" t="n">
-        <v>46.64090163934426</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N28" t="n">
-        <v>45.53188524590167</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O28" t="n">
-        <v>42.05606557377051</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P28" t="n">
-        <v>35.98622950819671</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q28" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R28" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S28" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T28" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U28" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H29" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I29" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J29" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K29" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L29" t="n">
-        <v>104.6763316582915</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M29" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N29" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O29" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P29" t="n">
-        <v>95.38575376884424</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q29" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R29" t="n">
-        <v>41.66706030150755</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S29" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T29" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U29" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,49 +33171,49 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H30" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I30" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J30" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K30" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L30" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M30" t="n">
-        <v>89.92499999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N30" t="n">
-        <v>92.30504716981135</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O30" t="n">
-        <v>84.44108490566038</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P30" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q30" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R30" t="n">
-        <v>22.03528301886794</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S30" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T30" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U30" t="n">
-        <v>0.0233490566037736</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H31" t="n">
-        <v>2.645409836065576</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I31" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J31" t="n">
-        <v>21.03614754098361</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K31" t="n">
-        <v>34.56885245901639</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L31" t="n">
-        <v>44.23622950819673</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M31" t="n">
-        <v>46.64090163934426</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N31" t="n">
-        <v>45.53188524590167</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O31" t="n">
-        <v>42.05606557377051</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P31" t="n">
-        <v>35.98622950819671</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q31" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R31" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S31" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T31" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H32" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I32" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J32" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K32" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L32" t="n">
-        <v>104.6763316582915</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M32" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N32" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O32" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P32" t="n">
-        <v>95.38575376884424</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q32" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R32" t="n">
-        <v>41.66706030150755</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S32" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T32" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U32" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,49 +33408,49 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H33" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I33" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J33" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K33" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L33" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M33" t="n">
-        <v>89.92499999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N33" t="n">
-        <v>92.30504716981135</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O33" t="n">
-        <v>84.44108490566038</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P33" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q33" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R33" t="n">
-        <v>22.03528301886794</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S33" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T33" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U33" t="n">
-        <v>0.0233490566037736</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H34" t="n">
-        <v>2.645409836065576</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I34" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J34" t="n">
-        <v>21.03614754098361</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K34" t="n">
-        <v>34.56885245901639</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L34" t="n">
-        <v>44.23622950819673</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M34" t="n">
-        <v>46.64090163934426</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N34" t="n">
-        <v>45.53188524590167</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O34" t="n">
-        <v>42.05606557377051</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P34" t="n">
-        <v>35.98622950819671</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q34" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R34" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S34" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T34" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U34" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H35" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I35" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J35" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K35" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L35" t="n">
-        <v>104.6763316582915</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M35" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N35" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O35" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P35" t="n">
-        <v>95.38575376884424</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q35" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R35" t="n">
-        <v>41.66706030150755</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S35" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T35" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U35" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,49 +33645,49 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H36" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I36" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J36" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K36" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L36" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M36" t="n">
-        <v>89.92499999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N36" t="n">
-        <v>92.30504716981135</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O36" t="n">
-        <v>84.44108490566038</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P36" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q36" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R36" t="n">
-        <v>22.03528301886794</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S36" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T36" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U36" t="n">
-        <v>0.0233490566037736</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H37" t="n">
-        <v>2.645409836065576</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I37" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J37" t="n">
-        <v>21.03614754098361</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K37" t="n">
-        <v>34.56885245901639</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L37" t="n">
-        <v>44.23622950819673</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M37" t="n">
-        <v>46.64090163934426</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N37" t="n">
-        <v>45.53188524590167</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O37" t="n">
-        <v>42.05606557377051</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P37" t="n">
-        <v>35.98622950819671</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q37" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R37" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S37" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T37" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U37" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H38" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I38" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J38" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K38" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L38" t="n">
-        <v>104.6763316582915</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M38" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N38" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O38" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P38" t="n">
-        <v>95.38575376884424</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q38" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R38" t="n">
-        <v>41.66706030150755</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S38" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T38" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U38" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,49 +33882,49 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H39" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I39" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J39" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K39" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L39" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M39" t="n">
-        <v>89.92499999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N39" t="n">
-        <v>92.30504716981135</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O39" t="n">
-        <v>84.44108490566038</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P39" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q39" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R39" t="n">
-        <v>22.03528301886794</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S39" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T39" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U39" t="n">
-        <v>0.0233490566037736</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H40" t="n">
-        <v>2.645409836065576</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I40" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J40" t="n">
-        <v>21.03614754098361</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K40" t="n">
-        <v>34.56885245901639</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L40" t="n">
-        <v>44.23622950819673</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M40" t="n">
-        <v>46.64090163934426</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N40" t="n">
-        <v>45.53188524590167</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O40" t="n">
-        <v>42.05606557377051</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P40" t="n">
-        <v>35.98622950819671</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q40" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R40" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S40" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T40" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U40" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H41" t="n">
-        <v>6.793190954773866</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I41" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J41" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K41" t="n">
-        <v>84.3763567839196</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L41" t="n">
-        <v>104.6763316582915</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M41" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N41" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O41" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P41" t="n">
-        <v>95.38575376884424</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q41" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R41" t="n">
-        <v>41.66706030150755</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S41" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T41" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U41" t="n">
-        <v>0.05306532663316578</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,49 +34119,49 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H42" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I42" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J42" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K42" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L42" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M42" t="n">
-        <v>89.92499999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N42" t="n">
-        <v>92.30504716981135</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O42" t="n">
-        <v>84.44108490566038</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P42" t="n">
-        <v>67.77141509433963</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q42" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R42" t="n">
-        <v>22.03528301886794</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S42" t="n">
-        <v>6.592216981132071</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T42" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U42" t="n">
-        <v>0.0233490566037736</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H43" t="n">
-        <v>2.645409836065576</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I43" t="n">
-        <v>8.947868852459019</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J43" t="n">
-        <v>21.03614754098361</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K43" t="n">
-        <v>34.56885245901639</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L43" t="n">
-        <v>44.23622950819673</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M43" t="n">
-        <v>46.64090163934426</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N43" t="n">
-        <v>45.53188524590167</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O43" t="n">
-        <v>42.05606557377051</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P43" t="n">
-        <v>35.98622950819671</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q43" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R43" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S43" t="n">
-        <v>5.185327868852457</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T43" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U43" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.6633165829145723</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H44" t="n">
-        <v>6.793190954773864</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I44" t="n">
-        <v>25.57251256281408</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J44" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K44" t="n">
-        <v>84.37635678391959</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L44" t="n">
-        <v>104.6763316582915</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M44" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N44" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O44" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P44" t="n">
-        <v>95.38575376884422</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q44" t="n">
-        <v>71.63072864321606</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R44" t="n">
-        <v>41.66706030150755</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S44" t="n">
-        <v>15.11532663316583</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T44" t="n">
-        <v>2.903668341708542</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U44" t="n">
-        <v>0.05306532663316577</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,49 +34356,49 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H45" t="n">
-        <v>3.427641509433963</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I45" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J45" t="n">
-        <v>33.53080188679245</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K45" t="n">
-        <v>57.30948113207548</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L45" t="n">
-        <v>77.05966981132076</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M45" t="n">
-        <v>89.92499999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N45" t="n">
-        <v>92.30504716981133</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O45" t="n">
-        <v>84.44108490566036</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P45" t="n">
-        <v>67.77141509433962</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q45" t="n">
-        <v>45.3033962264151</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R45" t="n">
-        <v>22.03528301886794</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S45" t="n">
-        <v>6.59221698113207</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T45" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U45" t="n">
-        <v>0.0233490566037736</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2975409836065573</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H46" t="n">
-        <v>2.645409836065576</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I46" t="n">
-        <v>8.947868852459017</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J46" t="n">
-        <v>21.0361475409836</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K46" t="n">
-        <v>34.56885245901638</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L46" t="n">
-        <v>44.23622950819672</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M46" t="n">
-        <v>46.64090163934426</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N46" t="n">
-        <v>45.53188524590167</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O46" t="n">
-        <v>42.0560655737705</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P46" t="n">
-        <v>35.98622950819671</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q46" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R46" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S46" t="n">
-        <v>5.185327868852456</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T46" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U46" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -34854,7 +34854,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.665334536937735e-16</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -34936,7 +34936,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-8.326672684688674e-17</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -35091,7 +35091,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.665334536937735e-16</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -35173,7 +35173,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.665334536937735e-16</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -35343,7 +35343,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.326672684688674e-17</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35407,7 +35407,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.665334536937735e-16</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -35489,7 +35489,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.665334536937735e-16</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -35580,7 +35580,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.387778780781446e-16</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35647,7 +35647,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.775557561562891e-16</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -35732,7 +35732,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.775557561562891e-16</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -36033,7 +36033,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -36048,13 +36048,13 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36118,7 +36118,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -36127,10 +36127,10 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -36194,22 +36194,22 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -36270,16 +36270,16 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -36288,7 +36288,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.35308431126191e-16</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36349,7 +36349,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -36358,19 +36358,19 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.318389841742373e-16</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36431,7 +36431,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -36440,13 +36440,13 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1.387778780781446e-16</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -36507,7 +36507,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -36522,13 +36522,13 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36586,28 +36586,28 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36668,22 +36668,22 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -36750,16 +36750,16 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -36835,16 +36835,16 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36905,7 +36905,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -36914,13 +36914,13 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -36990,19 +36990,19 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37069,13 +37069,13 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -37142,13 +37142,13 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -37157,7 +37157,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -37218,7 +37218,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -37233,13 +37233,13 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37303,16 +37303,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -37379,13 +37379,13 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -37394,7 +37394,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -37455,10 +37455,10 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -37473,10 +37473,10 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37534,7 +37534,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -37549,13 +37549,13 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37616,22 +37616,22 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -37701,7 +37701,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -37774,7 +37774,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -37859,7 +37859,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
